--- a/qc/spreadsheets/trust_qc.xlsx
+++ b/qc/spreadsheets/trust_qc.xlsx
@@ -11,7 +11,7 @@
     <sheet name="thresholds" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'runs'!$A$1:$Y$650</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'runs'!$A$1:$Y$652</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'thresholds'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y650"/>
+  <dimension ref="A1:Y652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -464,8 +464,8 @@
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="45" customWidth="1" min="24" max="24"/>
@@ -16692,26 +16692,42 @@
       <c r="G178" t="n">
         <v>0.1854251588398254</v>
       </c>
+      <c r="H178" t="n">
+        <v>21</v>
+      </c>
+      <c r="I178" t="n">
+        <v>11</v>
+      </c>
+      <c r="J178" t="n">
+        <v>10</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="L178" t="n">
+        <v>99.98538710877305</v>
+      </c>
       <c r="M178" t="b">
         <v>0</v>
       </c>
       <c r="N178" t="b">
         <v>0</v>
       </c>
+      <c r="O178" t="b">
+        <v>0</v>
+      </c>
+      <c r="P178" t="b">
+        <v>0</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
       <c r="S178" t="b">
-        <v>0</v>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>brain_coverage_pct:missing_fmriprep_brain_mask;tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
@@ -16722,6 +16738,16 @@
       <c r="W178" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-10929/ses-01/func/sub-10929_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-10929/ses-01/sub-10929_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>derivatives/fmriprep/sub-10929/ses-01/func/sub-10929_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
@@ -23913,7 +23939,7 @@
         <v>0.1212121212121212</v>
       </c>
       <c r="L257" t="n">
-        <v>99.81003241404963</v>
+        <v>99.77416440831075</v>
       </c>
       <c r="M257" t="b">
         <v>0</v>
@@ -24004,7 +24030,7 @@
         <v>0.1875</v>
       </c>
       <c r="L258" t="n">
-        <v>99.81800308199161</v>
+        <v>99.81667463733461</v>
       </c>
       <c r="M258" t="b">
         <v>0</v>
@@ -24095,7 +24121,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="L259" t="n">
-        <v>99.50449014294064</v>
+        <v>99.46862213720176</v>
       </c>
       <c r="M259" t="b">
         <v>0</v>
@@ -24191,7 +24217,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="L260" t="n">
-        <v>99.88043998087039</v>
+        <v>99.86848397895744</v>
       </c>
       <c r="M260" t="b">
         <v>0</v>
@@ -24282,7 +24308,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="L261" t="n">
-        <v>99.86317020032945</v>
+        <v>99.84988575375949</v>
       </c>
       <c r="M261" t="b">
         <v>0</v>
@@ -51307,17 +51333,22 @@
         <v>0</v>
       </c>
       <c r="P554" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q554" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>low_brain_coverage</t>
+        </is>
       </c>
       <c r="S554" t="b">
         <v>1</v>
       </c>
       <c r="U554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V554" t="inlineStr">
@@ -57537,7 +57568,7 @@
         <v>0.6575342465753424</v>
       </c>
       <c r="L621" t="n">
-        <v>99.73591549295774</v>
+        <v>99.73298262394388</v>
       </c>
       <c r="M621" t="b">
         <v>0</v>
@@ -57633,7 +57664,7 @@
         <v>0.7384615384615385</v>
       </c>
       <c r="L622" t="n">
-        <v>99.72391165172856</v>
+        <v>99.71704128805995</v>
       </c>
       <c r="M622" t="b">
         <v>0</v>
@@ -57687,7 +57718,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -57711,25 +57742,25 @@
         </is>
       </c>
       <c r="F623" t="n">
-        <v>57.47942130547017</v>
+        <v>42.94423284055665</v>
       </c>
       <c r="G623" t="n">
-        <v>0.1033781293569549</v>
+        <v>0.2172655514384385</v>
       </c>
       <c r="H623" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I623" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J623" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K623" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="L623" t="n">
-        <v>99.01030873053828</v>
+        <v>99.97608799617407</v>
       </c>
       <c r="M623" t="b">
         <v>0</v>
@@ -57741,49 +57772,44 @@
         <v>0</v>
       </c>
       <c r="P623" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q623" t="b">
-        <v>1</v>
-      </c>
-      <c r="R623" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S623" t="b">
         <v>1</v>
       </c>
       <c r="U623" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V623" t="inlineStr">
         <is>
-          <t>bids/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12018/ses-01/func/sub-12018_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W623" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12018/ses-01/func/sub-12018_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X623" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12020/ses-01/sub-12020_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12018/ses-01/sub-12018_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y623" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12018/ses-01/func/sub-12018_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -57807,25 +57833,25 @@
         </is>
       </c>
       <c r="F624" t="n">
-        <v>54.08577603264712</v>
+        <v>42.34432117827237</v>
       </c>
       <c r="G624" t="n">
-        <v>0.1006281650481061</v>
+        <v>0.2223697326605351</v>
       </c>
       <c r="H624" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I624" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J624" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K624" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="L624" t="n">
-        <v>99.15378075349381</v>
+        <v>99.96811732823211</v>
       </c>
       <c r="M624" t="b">
         <v>0</v>
@@ -57837,49 +57863,44 @@
         <v>0</v>
       </c>
       <c r="P624" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q624" t="b">
-        <v>1</v>
-      </c>
-      <c r="R624" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S624" t="b">
         <v>1</v>
       </c>
       <c r="U624" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V624" t="inlineStr">
         <is>
-          <t>bids/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12018/ses-01/func/sub-12018_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W624" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12018/ses-01/func/sub-12018_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X624" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12020/ses-01/sub-12020_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12018/ses-01/sub-12018_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y624" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12018/ses-01/func/sub-12018_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -57903,25 +57924,25 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>35.53053482528776</v>
+        <v>57.47942130547017</v>
       </c>
       <c r="G625" t="n">
-        <v>0.1164891821378112</v>
+        <v>0.1033781293569549</v>
       </c>
       <c r="H625" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="I625" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J625" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="K625" t="n">
-        <v>0.671875</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="L625" t="n">
-        <v>99.75025240448483</v>
+        <v>99.01030873053828</v>
       </c>
       <c r="M625" t="b">
         <v>0</v>
@@ -57930,17 +57951,17 @@
         <v>0</v>
       </c>
       <c r="O625" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P625" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q625" t="b">
         <v>1</v>
       </c>
       <c r="R625" t="inlineStr">
         <is>
-          <t>high_tedana_rejected_components</t>
+          <t>low_brain_coverage</t>
         </is>
       </c>
       <c r="S625" t="b">
@@ -57953,29 +57974,29 @@
       </c>
       <c r="V625" t="inlineStr">
         <is>
-          <t>bids/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W625" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X625" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12021/ses-01/sub-12021_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12020/ses-01/sub-12020_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y625" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -57999,25 +58020,25 @@
         </is>
       </c>
       <c r="F626" t="n">
-        <v>32.20928612223361</v>
+        <v>54.08577603264712</v>
       </c>
       <c r="G626" t="n">
-        <v>0.1579267020575461</v>
+        <v>0.1006281650481061</v>
       </c>
       <c r="H626" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I626" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J626" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="K626" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="L626" t="n">
-        <v>99.72501195600191</v>
+        <v>99.15378075349381</v>
       </c>
       <c r="M626" t="b">
         <v>0</v>
@@ -58026,17 +58047,17 @@
         <v>0</v>
       </c>
       <c r="O626" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P626" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q626" t="b">
         <v>1</v>
       </c>
       <c r="R626" t="inlineStr">
         <is>
-          <t>high_tedana_rejected_components</t>
+          <t>low_brain_coverage</t>
         </is>
       </c>
       <c r="S626" t="b">
@@ -58049,29 +58070,29 @@
       </c>
       <c r="V626" t="inlineStr">
         <is>
-          <t>bids/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W626" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X626" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12021/ses-01/sub-12021_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12020/ses-01/sub-12020_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y626" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12020/ses-01/func/sub-12020_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -58095,25 +58116,25 @@
         </is>
       </c>
       <c r="F627" t="n">
-        <v>41.24953425675631</v>
+        <v>35.53053482528776</v>
       </c>
       <c r="G627" t="n">
-        <v>0.1245780892789839</v>
+        <v>0.1164891821378112</v>
       </c>
       <c r="H627" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="I627" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J627" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K627" t="n">
-        <v>0.62</v>
+        <v>0.671875</v>
       </c>
       <c r="L627" t="n">
-        <v>99.82730219459057</v>
+        <v>99.75025240448483</v>
       </c>
       <c r="M627" t="b">
         <v>0</v>
@@ -58122,47 +58143,52 @@
         <v>0</v>
       </c>
       <c r="O627" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P627" t="b">
         <v>0</v>
       </c>
       <c r="Q627" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>high_tedana_rejected_components</t>
+        </is>
       </c>
       <c r="S627" t="b">
         <v>1</v>
       </c>
       <c r="U627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V627" t="inlineStr">
         <is>
-          <t>bids/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W627" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X627" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12031/ses-01/sub-12031_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12021/ses-01/sub-12021_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y627" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -58186,25 +58212,25 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>38.8435785472393</v>
+        <v>32.20928612223361</v>
       </c>
       <c r="G628" t="n">
-        <v>0.1492606187758891</v>
+        <v>0.1579267020575461</v>
       </c>
       <c r="H628" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="I628" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J628" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="K628" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="L628" t="n">
-        <v>99.6399914979542</v>
+        <v>99.72501195600191</v>
       </c>
       <c r="M628" t="b">
         <v>0</v>
@@ -58236,29 +58262,29 @@
       </c>
       <c r="V628" t="inlineStr">
         <is>
-          <t>bids/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W628" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X628" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12031/ses-01/sub-12031_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12021/ses-01/sub-12021_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y628" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12021/ses-01/func/sub-12021_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -58282,25 +58308,25 @@
         </is>
       </c>
       <c r="F629" t="n">
-        <v>46.27398584969342</v>
+        <v>41.24953425675631</v>
       </c>
       <c r="G629" t="n">
-        <v>0.1755799144999427</v>
+        <v>0.1245780892789839</v>
       </c>
       <c r="H629" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I629" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J629" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K629" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.62</v>
       </c>
       <c r="L629" t="n">
-        <v>99.94287687974919</v>
+        <v>99.82730219459057</v>
       </c>
       <c r="M629" t="b">
         <v>0</v>
@@ -58327,29 +58353,29 @@
       </c>
       <c r="V629" t="inlineStr">
         <is>
-          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W629" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X629" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12031/ses-01/sub-12031_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y629" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -58373,25 +58399,25 @@
         </is>
       </c>
       <c r="F630" t="n">
-        <v>41.97511292528361</v>
+        <v>38.8435785472393</v>
       </c>
       <c r="G630" t="n">
-        <v>0.1949855399796346</v>
+        <v>0.1492606187758891</v>
       </c>
       <c r="H630" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I630" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J630" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K630" t="n">
-        <v>0.6382978723404256</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="L630" t="n">
-        <v>99.93224932249322</v>
+        <v>99.6399914979542</v>
       </c>
       <c r="M630" t="b">
         <v>0</v>
@@ -58400,47 +58426,52 @@
         <v>0</v>
       </c>
       <c r="O630" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P630" t="b">
         <v>0</v>
       </c>
       <c r="Q630" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>high_tedana_rejected_components</t>
+        </is>
       </c>
       <c r="S630" t="b">
         <v>1</v>
       </c>
       <c r="U630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V630" t="inlineStr">
         <is>
-          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W630" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X630" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12031/ses-01/sub-12031_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y630" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12031/ses-01/func/sub-12031_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -58464,25 +58495,25 @@
         </is>
       </c>
       <c r="F631" t="n">
-        <v>31.27213206142187</v>
+        <v>46.27398584969342</v>
       </c>
       <c r="G631" t="n">
-        <v>0.218832891296666</v>
+        <v>0.1755799144999427</v>
       </c>
       <c r="H631" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I631" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J631" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K631" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L631" t="n">
-        <v>99.37164567724109</v>
+        <v>99.94287687974919</v>
       </c>
       <c r="M631" t="b">
         <v>0</v>
@@ -58509,29 +58540,29 @@
       </c>
       <c r="V631" t="inlineStr">
         <is>
-          <t>bids/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W631" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X631" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12036/ses-01/sub-12036_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y631" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -58551,29 +58582,29 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F632" t="n">
-        <v>50.3094316595234</v>
+        <v>41.97511292528361</v>
       </c>
       <c r="G632" t="n">
-        <v>0.1309292105990445</v>
+        <v>0.1949855399796346</v>
       </c>
       <c r="H632" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I632" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J632" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K632" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.6382978723404256</v>
       </c>
       <c r="L632" t="n">
-        <v>99.50449014294064</v>
+        <v>99.93224932249322</v>
       </c>
       <c r="M632" t="b">
         <v>0</v>
@@ -58600,29 +58631,29 @@
       </c>
       <c r="V632" t="inlineStr">
         <is>
-          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W632" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X632" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y632" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -58642,29 +58673,29 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F633" t="n">
-        <v>55.27668376103975</v>
+        <v>31.27213206142187</v>
       </c>
       <c r="G633" t="n">
-        <v>0.09780495405193819</v>
+        <v>0.218832891296666</v>
       </c>
       <c r="H633" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I633" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J633" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K633" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L633" t="n">
-        <v>99.47526436048675</v>
+        <v>99.37164567724109</v>
       </c>
       <c r="M633" t="b">
         <v>0</v>
@@ -58691,29 +58722,29 @@
       </c>
       <c r="V633" t="inlineStr">
         <is>
-          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W633" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X633" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12036/ses-01/sub-12036_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y633" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -58737,25 +58768,25 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>60.04252373240888</v>
+        <v>50.3094316595234</v>
       </c>
       <c r="G634" t="n">
-        <v>0.08220573391182444</v>
+        <v>0.1309292105990445</v>
       </c>
       <c r="H634" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="I634" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="J634" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K634" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="L634" t="n">
-        <v>99.33444922684521</v>
+        <v>99.50449014294064</v>
       </c>
       <c r="M634" t="b">
         <v>0</v>
@@ -58782,29 +58813,29 @@
       </c>
       <c r="V634" t="inlineStr">
         <is>
-          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W634" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X634" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y634" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -58828,25 +58859,25 @@
         </is>
       </c>
       <c r="F635" t="n">
-        <v>57.46608637506142</v>
+        <v>55.27668376103975</v>
       </c>
       <c r="G635" t="n">
-        <v>0.08071037414415071</v>
+        <v>0.09780495405193819</v>
       </c>
       <c r="H635" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I635" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J635" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K635" t="n">
-        <v>0.55</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="L635" t="n">
-        <v>99.42478346352091</v>
+        <v>99.47526436048675</v>
       </c>
       <c r="M635" t="b">
         <v>0</v>
@@ -58873,29 +58904,29 @@
       </c>
       <c r="V635" t="inlineStr">
         <is>
-          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W635" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X635" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y635" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -58919,25 +58950,25 @@
         </is>
       </c>
       <c r="F636" t="n">
-        <v>53.40385221643373</v>
+        <v>60.04252373240888</v>
       </c>
       <c r="G636" t="n">
-        <v>0.1351599856617334</v>
+        <v>0.08220573391182444</v>
       </c>
       <c r="H636" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I636" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J636" t="n">
         <v>10</v>
       </c>
       <c r="K636" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="L636" t="n">
-        <v>99.68117328232105</v>
+        <v>99.33444922684521</v>
       </c>
       <c r="M636" t="b">
         <v>0</v>
@@ -58964,29 +58995,29 @@
       </c>
       <c r="V636" t="inlineStr">
         <is>
-          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W636" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X636" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -59010,25 +59041,25 @@
         </is>
       </c>
       <c r="F637" t="n">
-        <v>59.27155510801822</v>
+        <v>57.46608637506142</v>
       </c>
       <c r="G637" t="n">
-        <v>0.14215089922922</v>
+        <v>0.08071037414415071</v>
       </c>
       <c r="H637" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I637" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J637" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K637" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.55</v>
       </c>
       <c r="L637" t="n">
-        <v>99.63202083001222</v>
+        <v>99.42478346352091</v>
       </c>
       <c r="M637" t="b">
         <v>0</v>
@@ -59055,29 +59086,29 @@
       </c>
       <c r="V637" t="inlineStr">
         <is>
-          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W637" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X637" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y637" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -59101,25 +59132,25 @@
         </is>
       </c>
       <c r="F638" t="n">
-        <v>49.98425288451836</v>
+        <v>53.40385221643373</v>
       </c>
       <c r="G638" t="n">
-        <v>0.1244745319377253</v>
+        <v>0.1351599856617334</v>
       </c>
       <c r="H638" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I638" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J638" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K638" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L638" t="n">
-        <v>99.47260747117275</v>
+        <v>99.68117328232105</v>
       </c>
       <c r="M638" t="b">
         <v>0</v>
@@ -59146,29 +59177,29 @@
       </c>
       <c r="V638" t="inlineStr">
         <is>
-          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W638" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X638" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y638" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -59192,25 +59223,25 @@
         </is>
       </c>
       <c r="F639" t="n">
-        <v>47.93555379635654</v>
+        <v>59.27155510801822</v>
       </c>
       <c r="G639" t="n">
-        <v>0.1637942983436465</v>
+        <v>0.14215089922922</v>
       </c>
       <c r="H639" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I639" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J639" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K639" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="L639" t="n">
-        <v>99.48190658377172</v>
+        <v>99.63202083001222</v>
       </c>
       <c r="M639" t="b">
         <v>0</v>
@@ -59237,29 +59268,29 @@
       </c>
       <c r="V639" t="inlineStr">
         <is>
-          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W639" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X639" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y639" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -59283,25 +59314,25 @@
         </is>
       </c>
       <c r="F640" t="n">
-        <v>44.67580807395279</v>
+        <v>49.98425288451836</v>
       </c>
       <c r="G640" t="n">
-        <v>0.09256886814108874</v>
+        <v>0.1244745319377253</v>
       </c>
       <c r="H640" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I640" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J640" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K640" t="n">
-        <v>0.5</v>
+        <v>0.71875</v>
       </c>
       <c r="L640" t="n">
-        <v>99.37430256655507</v>
+        <v>99.47260747117275</v>
       </c>
       <c r="M640" t="b">
         <v>0</v>
@@ -59328,29 +59359,29 @@
       </c>
       <c r="V640" t="inlineStr">
         <is>
-          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W640" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X640" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y640" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -59374,25 +59405,25 @@
         </is>
       </c>
       <c r="F641" t="n">
-        <v>38.64221795392223</v>
+        <v>47.93555379635654</v>
       </c>
       <c r="G641" t="n">
-        <v>0.09465885902386993</v>
+        <v>0.1637942983436465</v>
       </c>
       <c r="H641" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="I641" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J641" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K641" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L641" t="n">
-        <v>99.39422923641001</v>
+        <v>99.48190658377172</v>
       </c>
       <c r="M641" t="b">
         <v>0</v>
@@ -59419,29 +59450,29 @@
       </c>
       <c r="V641" t="inlineStr">
         <is>
-          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W641" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X641" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y641" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -59465,25 +59496,25 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>30.91064093692694</v>
+        <v>44.67580807395279</v>
       </c>
       <c r="G642" t="n">
-        <v>0.3061122550998683</v>
+        <v>0.09256886814108874</v>
       </c>
       <c r="H642" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="I642" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J642" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="K642" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.5</v>
       </c>
       <c r="L642" t="n">
-        <v>99.70242839683299</v>
+        <v>99.37430256655507</v>
       </c>
       <c r="M642" t="b">
         <v>0</v>
@@ -59492,52 +59523,47 @@
         <v>0</v>
       </c>
       <c r="O642" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P642" t="b">
         <v>0</v>
       </c>
       <c r="Q642" t="b">
-        <v>1</v>
-      </c>
-      <c r="R642" t="inlineStr">
-        <is>
-          <t>high_tedana_rejected_components</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S642" t="b">
         <v>1</v>
       </c>
       <c r="U642" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V642" t="inlineStr">
         <is>
-          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W642" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X642" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y642" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -59561,25 +59587,25 @@
         </is>
       </c>
       <c r="F643" t="n">
-        <v>28.32871760160197</v>
+        <v>38.64221795392223</v>
       </c>
       <c r="G643" t="n">
-        <v>0.2903349328589003</v>
+        <v>0.09465885902386993</v>
       </c>
       <c r="H643" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="I643" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J643" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="K643" t="n">
-        <v>0.78</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="L643" t="n">
-        <v>99.6399914979542</v>
+        <v>99.39422923641001</v>
       </c>
       <c r="M643" t="b">
         <v>0</v>
@@ -59588,52 +59614,47 @@
         <v>0</v>
       </c>
       <c r="O643" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P643" t="b">
         <v>0</v>
       </c>
       <c r="Q643" t="b">
-        <v>1</v>
-      </c>
-      <c r="R643" t="inlineStr">
-        <is>
-          <t>high_tedana_rejected_components</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S643" t="b">
         <v>1</v>
       </c>
       <c r="U643" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V643" t="inlineStr">
         <is>
-          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W643" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X643" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y643" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -59657,25 +59678,25 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>53.49885014863685</v>
+        <v>30.91064093692694</v>
       </c>
       <c r="G644" t="n">
-        <v>0.1332510791776314</v>
+        <v>0.3061122550998683</v>
       </c>
       <c r="H644" t="n">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="I644" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J644" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="K644" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="L644" t="n">
-        <v>99.14846697486583</v>
+        <v>99.70242839683299</v>
       </c>
       <c r="M644" t="b">
         <v>0</v>
@@ -59684,17 +59705,17 @@
         <v>0</v>
       </c>
       <c r="O644" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P644" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q644" t="b">
         <v>1</v>
       </c>
       <c r="R644" t="inlineStr">
         <is>
-          <t>low_brain_coverage</t>
+          <t>high_tedana_rejected_components</t>
         </is>
       </c>
       <c r="S644" t="b">
@@ -59707,29 +59728,29 @@
       </c>
       <c r="V644" t="inlineStr">
         <is>
-          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W644" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X644" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y644" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -59753,25 +59774,25 @@
         </is>
       </c>
       <c r="F645" t="n">
-        <v>48.44328886829317</v>
+        <v>28.32871760160197</v>
       </c>
       <c r="G645" t="n">
-        <v>0.144711205721414</v>
+        <v>0.2903349328589003</v>
       </c>
       <c r="H645" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I645" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J645" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="K645" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="L645" t="n">
-        <v>99.61209416015728</v>
+        <v>99.6399914979542</v>
       </c>
       <c r="M645" t="b">
         <v>0</v>
@@ -59780,47 +59801,52 @@
         <v>0</v>
       </c>
       <c r="O645" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P645" t="b">
         <v>0</v>
       </c>
       <c r="Q645" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>high_tedana_rejected_components</t>
+        </is>
       </c>
       <c r="S645" t="b">
         <v>1</v>
       </c>
       <c r="U645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V645" t="inlineStr">
         <is>
-          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W645" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X645" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y645" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -59844,25 +59870,25 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>45.51768332021311</v>
+        <v>53.49885014863685</v>
       </c>
       <c r="G646" t="n">
-        <v>0.1415992202242452</v>
+        <v>0.1332510791776314</v>
       </c>
       <c r="H646" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I646" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J646" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K646" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L646" t="n">
-        <v>98.70742334874329</v>
+        <v>99.14846697486583</v>
       </c>
       <c r="M646" t="b">
         <v>0</v>
@@ -59894,29 +59920,29 @@
       </c>
       <c r="V646" t="inlineStr">
         <is>
-          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W646" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X646" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y646" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -59940,25 +59966,25 @@
         </is>
       </c>
       <c r="F647" t="n">
-        <v>53.94919102569111</v>
+        <v>48.44328886829317</v>
       </c>
       <c r="G647" t="n">
-        <v>0.1026628483699073</v>
+        <v>0.144711205721414</v>
       </c>
       <c r="H647" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I647" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J647" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K647" t="n">
-        <v>0.525</v>
+        <v>0.5</v>
       </c>
       <c r="L647" t="n">
-        <v>98.96514161220044</v>
+        <v>99.61209416015728</v>
       </c>
       <c r="M647" t="b">
         <v>0</v>
@@ -59970,49 +59996,44 @@
         <v>0</v>
       </c>
       <c r="P647" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q647" t="b">
-        <v>1</v>
-      </c>
-      <c r="R647" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S647" t="b">
         <v>1</v>
       </c>
       <c r="U647" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V647" t="inlineStr">
         <is>
-          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W647" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X647" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -60036,25 +60057,25 @@
         </is>
       </c>
       <c r="F648" t="n">
-        <v>51.80856852419674</v>
+        <v>45.51768332021311</v>
       </c>
       <c r="G648" t="n">
-        <v>0.09047883923297501</v>
+        <v>0.1415992202242452</v>
       </c>
       <c r="H648" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="I648" t="n">
         <v>17</v>
       </c>
       <c r="J648" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K648" t="n">
-        <v>0.32</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="L648" t="n">
-        <v>99.78612041022372</v>
+        <v>98.70742334874329</v>
       </c>
       <c r="M648" t="b">
         <v>0</v>
@@ -60066,44 +60087,49 @@
         <v>0</v>
       </c>
       <c r="P648" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q648" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>low_brain_coverage</t>
+        </is>
       </c>
       <c r="S648" t="b">
         <v>1</v>
       </c>
       <c r="U648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V648" t="inlineStr">
         <is>
-          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W648" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X648" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -60127,25 +60153,25 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>54.0980097935535</v>
+        <v>53.94919102569111</v>
       </c>
       <c r="G649" t="n">
-        <v>0.104961722701671</v>
+        <v>0.1026628483699073</v>
       </c>
       <c r="H649" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I649" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J649" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K649" t="n">
-        <v>0.391304347826087</v>
+        <v>0.525</v>
       </c>
       <c r="L649" t="n">
-        <v>99.83925819650354</v>
+        <v>98.96514161220044</v>
       </c>
       <c r="M649" t="b">
         <v>0</v>
@@ -60157,134 +60183,321 @@
         <v>0</v>
       </c>
       <c r="P649" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q649" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>low_brain_coverage</t>
+        </is>
       </c>
       <c r="S649" t="b">
         <v>1</v>
       </c>
       <c r="U649" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V649" t="inlineStr">
         <is>
-          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W649" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X649" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y649" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
+          <t>12055</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>51.80856852419674</v>
+      </c>
+      <c r="G650" t="n">
+        <v>0.09047883923297501</v>
+      </c>
+      <c r="H650" t="n">
+        <v>25</v>
+      </c>
+      <c r="I650" t="n">
+        <v>17</v>
+      </c>
+      <c r="J650" t="n">
+        <v>8</v>
+      </c>
+      <c r="K650" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L650" t="n">
+        <v>99.78612041022372</v>
+      </c>
+      <c r="M650" t="b">
+        <v>0</v>
+      </c>
+      <c r="N650" t="b">
+        <v>0</v>
+      </c>
+      <c r="O650" t="b">
+        <v>0</v>
+      </c>
+      <c r="P650" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q650" t="b">
+        <v>0</v>
+      </c>
+      <c r="S650" t="b">
+        <v>1</v>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+        </is>
+      </c>
+      <c r="W650" t="inlineStr">
+        <is>
+          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X650" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+        </is>
+      </c>
+      <c r="Y650" t="inlineStr">
+        <is>
+          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>12055</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F651" t="n">
+        <v>54.0980097935535</v>
+      </c>
+      <c r="G651" t="n">
+        <v>0.104961722701671</v>
+      </c>
+      <c r="H651" t="n">
+        <v>23</v>
+      </c>
+      <c r="I651" t="n">
+        <v>14</v>
+      </c>
+      <c r="J651" t="n">
+        <v>9</v>
+      </c>
+      <c r="K651" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="L651" t="n">
+        <v>99.83925819650354</v>
+      </c>
+      <c r="M651" t="b">
+        <v>0</v>
+      </c>
+      <c r="N651" t="b">
+        <v>0</v>
+      </c>
+      <c r="O651" t="b">
+        <v>0</v>
+      </c>
+      <c r="P651" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q651" t="b">
+        <v>0</v>
+      </c>
+      <c r="S651" t="b">
+        <v>1</v>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+        </is>
+      </c>
+      <c r="W651" t="inlineStr">
+        <is>
+          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+        </is>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
           <t>12057</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="D650" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="E650" t="inlineStr">
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F650" t="n">
+      <c r="F652" t="n">
         <v>65.82148309098557</v>
       </c>
-      <c r="G650" t="n">
+      <c r="G652" t="n">
         <v>0.08265729611933353</v>
       </c>
-      <c r="H650" t="n">
+      <c r="H652" t="n">
         <v>27</v>
       </c>
-      <c r="I650" t="n">
+      <c r="I652" t="n">
         <v>14</v>
       </c>
-      <c r="J650" t="n">
+      <c r="J652" t="n">
         <v>13</v>
       </c>
-      <c r="K650" t="n">
+      <c r="K652" t="n">
         <v>0.4814814814814815</v>
       </c>
-      <c r="L650" t="n">
+      <c r="L652" t="n">
         <v>99.29326744247835</v>
       </c>
-      <c r="M650" t="b">
-        <v>0</v>
-      </c>
-      <c r="N650" t="b">
-        <v>0</v>
-      </c>
-      <c r="O650" t="b">
-        <v>0</v>
-      </c>
-      <c r="P650" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q650" t="b">
-        <v>0</v>
-      </c>
-      <c r="S650" t="b">
-        <v>1</v>
-      </c>
-      <c r="U650" t="inlineStr">
+      <c r="M652" t="b">
+        <v>0</v>
+      </c>
+      <c r="N652" t="b">
+        <v>0</v>
+      </c>
+      <c r="O652" t="b">
+        <v>0</v>
+      </c>
+      <c r="P652" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q652" t="b">
+        <v>0</v>
+      </c>
+      <c r="S652" t="b">
+        <v>1</v>
+      </c>
+      <c r="U652" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="V650" t="inlineStr">
+      <c r="V652" t="inlineStr">
         <is>
           <t>bids/sub-12057/ses-01/func/sub-12057_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
-      <c r="W650" t="inlineStr">
+      <c r="W652" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-12057/ses-01/func/sub-12057_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
-      <c r="X650" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>derivatives/tedana/sub-12057/ses-01/sub-12057_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
-      <c r="Y650" t="inlineStr">
+      <c r="Y652" t="inlineStr">
         <is>
           <t>derivatives/fmriprep/sub-12057/ses-01/func/sub-12057_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y650"/>
-  <conditionalFormatting sqref="A2:Y650">
+  <autoFilter ref="A1:Y652"/>
+  <conditionalFormatting sqref="A2:Y652">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$Q2=TRUE</formula>
     </cfRule>
@@ -60310,7 +60523,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -60392,22 +60605,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E2" t="n">
-        <v>23.4767181747593</v>
+        <v>23.60912652261322</v>
       </c>
       <c r="F2" t="n">
-        <v>39.15460362192243</v>
+        <v>39.1948999002343</v>
       </c>
       <c r="G2" t="n">
-        <v>15.67788544716313</v>
+        <v>15.58577337762108</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04010999598540366</v>
+        <v>0.2304664561816026</v>
       </c>
       <c r="I2" t="n">
-        <v>62.67143179266714</v>
+        <v>62.57355996666593</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -60435,22 +60648,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1236041402797409</v>
+        <v>0.1237710602220436</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2460278713548141</v>
+        <v>0.245989755381984</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1224237310750732</v>
+        <v>0.1222186951599404</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06003145633286891</v>
+        <v>-0.05955698251786697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4296634679674239</v>
+        <v>0.4293177981218946</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -60478,22 +60691,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>-9</v>
+        <v>-9.75</v>
       </c>
       <c r="I4" t="n">
-        <v>39</v>
+        <v>40.25</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -60521,22 +60734,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E5" t="n">
-        <v>99.61707582762102</v>
+        <v>99.61873638344227</v>
       </c>
       <c r="F5" t="n">
-        <v>99.90833731866731</v>
+        <v>99.9096657633243</v>
       </c>
       <c r="G5" t="n">
-        <v>0.291261491046285</v>
+        <v>0.29092937988203</v>
       </c>
       <c r="H5" t="n">
-        <v>99.18018359105159</v>
+        <v>99.18234231361922</v>
       </c>
       <c r="I5" t="n">
-        <v>100.3452295552367</v>
+        <v>100.3460598331473</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -60544,7 +60757,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/qc/spreadsheets/trust_qc.xlsx
+++ b/qc/spreadsheets/trust_qc.xlsx
@@ -11,7 +11,7 @@
     <sheet name="thresholds" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'runs'!$A$1:$Y$652</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'runs'!$A$1:$Y$654</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'thresholds'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y652"/>
+  <dimension ref="A1:Y654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25319,7 +25319,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="L272" t="n">
-        <v>99.74493862585685</v>
+        <v>99.73298262394388</v>
       </c>
       <c r="M272" t="b">
         <v>0</v>
@@ -25410,7 +25410,7 @@
         <v>0.3</v>
       </c>
       <c r="L273" t="n">
-        <v>99.75025240448483</v>
+        <v>99.72501195600191</v>
       </c>
       <c r="M273" t="b">
         <v>0</v>
@@ -44229,25 +44229,20 @@
         <v>0</v>
       </c>
       <c r="O478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P478" t="b">
         <v>0</v>
       </c>
       <c r="Q478" t="b">
-        <v>1</v>
-      </c>
-      <c r="R478" t="inlineStr">
-        <is>
-          <t>high_tedana_rejected_components</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S478" t="b">
         <v>1</v>
       </c>
       <c r="U478" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V478" t="inlineStr">
@@ -46850,22 +46845,17 @@
         <v>0</v>
       </c>
       <c r="P506" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q506" t="b">
-        <v>1</v>
-      </c>
-      <c r="R506" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S506" t="b">
         <v>1</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V506" t="inlineStr">
@@ -48707,25 +48697,20 @@
         <v>0</v>
       </c>
       <c r="O526" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P526" t="b">
         <v>0</v>
       </c>
       <c r="Q526" t="b">
-        <v>1</v>
-      </c>
-      <c r="R526" t="inlineStr">
-        <is>
-          <t>high_tedana_rejected_components</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S526" t="b">
         <v>1</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V526" t="inlineStr">
@@ -49357,22 +49342,17 @@
         <v>0</v>
       </c>
       <c r="P533" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q533" t="b">
-        <v>1</v>
-      </c>
-      <c r="R533" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S533" t="b">
         <v>1</v>
       </c>
       <c r="U533" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V533" t="inlineStr">
@@ -51333,22 +51313,17 @@
         <v>0</v>
       </c>
       <c r="P554" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q554" t="b">
-        <v>1</v>
-      </c>
-      <c r="R554" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S554" t="b">
         <v>1</v>
       </c>
       <c r="U554" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V554" t="inlineStr">
@@ -58471,7 +58446,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -58495,25 +58470,25 @@
         </is>
       </c>
       <c r="F631" t="n">
-        <v>46.27398584969342</v>
+        <v>39.7591680730693</v>
       </c>
       <c r="G631" t="n">
-        <v>0.1755799144999427</v>
+        <v>0.227561270688776</v>
       </c>
       <c r="H631" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I631" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J631" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K631" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="L631" t="n">
-        <v>99.94287687974919</v>
+        <v>99.40087145969498</v>
       </c>
       <c r="M631" t="b">
         <v>0</v>
@@ -58540,29 +58515,29 @@
       </c>
       <c r="V631" t="inlineStr">
         <is>
-          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12032/ses-01/func/sub-12032_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W631" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12032/ses-01/func/sub-12032_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X631" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12032/ses-01/sub-12032_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y631" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12032/ses-01/func/sub-12032_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -58586,25 +58561,25 @@
         </is>
       </c>
       <c r="F632" t="n">
-        <v>41.97511292528361</v>
+        <v>34.96752779034432</v>
       </c>
       <c r="G632" t="n">
-        <v>0.1949855399796346</v>
+        <v>0.2201096105026466</v>
       </c>
       <c r="H632" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I632" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J632" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K632" t="n">
-        <v>0.6382978723404256</v>
+        <v>0.7</v>
       </c>
       <c r="L632" t="n">
-        <v>99.93224932249322</v>
+        <v>99.3052234443913</v>
       </c>
       <c r="M632" t="b">
         <v>0</v>
@@ -58631,29 +58606,29 @@
       </c>
       <c r="V632" t="inlineStr">
         <is>
-          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12032/ses-01/func/sub-12032_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W632" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12032/ses-01/func/sub-12032_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X632" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12032/ses-01/sub-12032_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y632" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12032/ses-01/func/sub-12032_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -58677,25 +58652,25 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>31.27213206142187</v>
+        <v>46.27398584969342</v>
       </c>
       <c r="G633" t="n">
-        <v>0.218832891296666</v>
+        <v>0.1755799144999427</v>
       </c>
       <c r="H633" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I633" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J633" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K633" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L633" t="n">
-        <v>99.37164567724109</v>
+        <v>99.94287687974919</v>
       </c>
       <c r="M633" t="b">
         <v>0</v>
@@ -58722,29 +58697,29 @@
       </c>
       <c r="V633" t="inlineStr">
         <is>
-          <t>bids/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W633" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X633" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12036/ses-01/sub-12036_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y633" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -58764,29 +58739,29 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F634" t="n">
-        <v>50.3094316595234</v>
+        <v>41.97511292528361</v>
       </c>
       <c r="G634" t="n">
-        <v>0.1309292105990445</v>
+        <v>0.1949855399796346</v>
       </c>
       <c r="H634" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I634" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J634" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K634" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.6382978723404256</v>
       </c>
       <c r="L634" t="n">
-        <v>99.50449014294064</v>
+        <v>99.93224932249322</v>
       </c>
       <c r="M634" t="b">
         <v>0</v>
@@ -58813,29 +58788,29 @@
       </c>
       <c r="V634" t="inlineStr">
         <is>
-          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W634" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X634" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12033/ses-01/sub-12033_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y634" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12033/ses-01/func/sub-12033_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -58855,29 +58830,29 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F635" t="n">
-        <v>55.27668376103975</v>
+        <v>31.27213206142187</v>
       </c>
       <c r="G635" t="n">
-        <v>0.09780495405193819</v>
+        <v>0.218832891296666</v>
       </c>
       <c r="H635" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I635" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J635" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K635" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L635" t="n">
-        <v>99.47526436048675</v>
+        <v>99.37164567724109</v>
       </c>
       <c r="M635" t="b">
         <v>0</v>
@@ -58904,29 +58879,29 @@
       </c>
       <c r="V635" t="inlineStr">
         <is>
-          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W635" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X635" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12036/ses-01/sub-12036_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y635" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12036/ses-01/func/sub-12036_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -58950,25 +58925,25 @@
         </is>
       </c>
       <c r="F636" t="n">
-        <v>60.04252373240888</v>
+        <v>50.3094316595234</v>
       </c>
       <c r="G636" t="n">
-        <v>0.08220573391182444</v>
+        <v>0.1309292105990445</v>
       </c>
       <c r="H636" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="I636" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="J636" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K636" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="L636" t="n">
-        <v>99.33444922684521</v>
+        <v>99.50449014294064</v>
       </c>
       <c r="M636" t="b">
         <v>0</v>
@@ -58995,29 +58970,29 @@
       </c>
       <c r="V636" t="inlineStr">
         <is>
-          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W636" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X636" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -59041,25 +59016,25 @@
         </is>
       </c>
       <c r="F637" t="n">
-        <v>57.46608637506142</v>
+        <v>55.27668376103975</v>
       </c>
       <c r="G637" t="n">
-        <v>0.08071037414415071</v>
+        <v>0.09780495405193819</v>
       </c>
       <c r="H637" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I637" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J637" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K637" t="n">
-        <v>0.55</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="L637" t="n">
-        <v>99.42478346352091</v>
+        <v>99.47526436048675</v>
       </c>
       <c r="M637" t="b">
         <v>0</v>
@@ -59086,29 +59061,29 @@
       </c>
       <c r="V637" t="inlineStr">
         <is>
-          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W637" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X637" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12037/ses-01/sub-12037_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y637" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12037/ses-01/func/sub-12037_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -59132,25 +59107,25 @@
         </is>
       </c>
       <c r="F638" t="n">
-        <v>53.40385221643373</v>
+        <v>60.04252373240888</v>
       </c>
       <c r="G638" t="n">
-        <v>0.1351599856617334</v>
+        <v>0.08220573391182444</v>
       </c>
       <c r="H638" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I638" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J638" t="n">
         <v>10</v>
       </c>
       <c r="K638" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="L638" t="n">
-        <v>99.68117328232105</v>
+        <v>99.33444922684521</v>
       </c>
       <c r="M638" t="b">
         <v>0</v>
@@ -59177,29 +59152,29 @@
       </c>
       <c r="V638" t="inlineStr">
         <is>
-          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W638" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X638" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y638" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -59223,25 +59198,25 @@
         </is>
       </c>
       <c r="F639" t="n">
-        <v>59.27155510801822</v>
+        <v>57.46608637506142</v>
       </c>
       <c r="G639" t="n">
-        <v>0.14215089922922</v>
+        <v>0.08071037414415071</v>
       </c>
       <c r="H639" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I639" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J639" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K639" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.55</v>
       </c>
       <c r="L639" t="n">
-        <v>99.63202083001222</v>
+        <v>99.42478346352091</v>
       </c>
       <c r="M639" t="b">
         <v>0</v>
@@ -59268,29 +59243,29 @@
       </c>
       <c r="V639" t="inlineStr">
         <is>
-          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W639" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X639" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12038/ses-01/sub-12038_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y639" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12038/ses-01/func/sub-12038_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -59314,25 +59289,25 @@
         </is>
       </c>
       <c r="F640" t="n">
-        <v>49.98425288451836</v>
+        <v>53.40385221643373</v>
       </c>
       <c r="G640" t="n">
-        <v>0.1244745319377253</v>
+        <v>0.1351599856617334</v>
       </c>
       <c r="H640" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I640" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J640" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K640" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L640" t="n">
-        <v>99.47260747117275</v>
+        <v>99.68117328232105</v>
       </c>
       <c r="M640" t="b">
         <v>0</v>
@@ -59359,29 +59334,29 @@
       </c>
       <c r="V640" t="inlineStr">
         <is>
-          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W640" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X640" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y640" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -59405,25 +59380,25 @@
         </is>
       </c>
       <c r="F641" t="n">
-        <v>47.93555379635654</v>
+        <v>59.27155510801822</v>
       </c>
       <c r="G641" t="n">
-        <v>0.1637942983436465</v>
+        <v>0.14215089922922</v>
       </c>
       <c r="H641" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I641" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J641" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K641" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="L641" t="n">
-        <v>99.48190658377172</v>
+        <v>99.63202083001222</v>
       </c>
       <c r="M641" t="b">
         <v>0</v>
@@ -59450,29 +59425,29 @@
       </c>
       <c r="V641" t="inlineStr">
         <is>
-          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W641" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X641" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12039/ses-01/sub-12039_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y641" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12039/ses-01/func/sub-12039_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -59496,25 +59471,25 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>44.67580807395279</v>
+        <v>49.98425288451836</v>
       </c>
       <c r="G642" t="n">
-        <v>0.09256886814108874</v>
+        <v>0.1244745319377253</v>
       </c>
       <c r="H642" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I642" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J642" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K642" t="n">
-        <v>0.5</v>
+        <v>0.71875</v>
       </c>
       <c r="L642" t="n">
-        <v>99.37430256655507</v>
+        <v>99.47260747117275</v>
       </c>
       <c r="M642" t="b">
         <v>0</v>
@@ -59541,29 +59516,29 @@
       </c>
       <c r="V642" t="inlineStr">
         <is>
-          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W642" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X642" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y642" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -59587,25 +59562,25 @@
         </is>
       </c>
       <c r="F643" t="n">
-        <v>38.64221795392223</v>
+        <v>47.93555379635654</v>
       </c>
       <c r="G643" t="n">
-        <v>0.09465885902386993</v>
+        <v>0.1637942983436465</v>
       </c>
       <c r="H643" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="I643" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J643" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K643" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L643" t="n">
-        <v>99.39422923641001</v>
+        <v>99.48190658377172</v>
       </c>
       <c r="M643" t="b">
         <v>0</v>
@@ -59632,29 +59607,29 @@
       </c>
       <c r="V643" t="inlineStr">
         <is>
-          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W643" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X643" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12041/ses-01/sub-12041_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y643" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12041/ses-01/func/sub-12041_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -59678,25 +59653,25 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>30.91064093692694</v>
+        <v>44.67580807395279</v>
       </c>
       <c r="G644" t="n">
-        <v>0.3061122550998683</v>
+        <v>0.09256886814108874</v>
       </c>
       <c r="H644" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="I644" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J644" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="K644" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.5</v>
       </c>
       <c r="L644" t="n">
-        <v>99.70242839683299</v>
+        <v>99.37430256655507</v>
       </c>
       <c r="M644" t="b">
         <v>0</v>
@@ -59705,52 +59680,47 @@
         <v>0</v>
       </c>
       <c r="O644" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P644" t="b">
         <v>0</v>
       </c>
       <c r="Q644" t="b">
-        <v>1</v>
-      </c>
-      <c r="R644" t="inlineStr">
-        <is>
-          <t>high_tedana_rejected_components</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S644" t="b">
         <v>1</v>
       </c>
       <c r="U644" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V644" t="inlineStr">
         <is>
-          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W644" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X644" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y644" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -59774,25 +59744,25 @@
         </is>
       </c>
       <c r="F645" t="n">
-        <v>28.32871760160197</v>
+        <v>38.64221795392223</v>
       </c>
       <c r="G645" t="n">
-        <v>0.2903349328589003</v>
+        <v>0.09465885902386993</v>
       </c>
       <c r="H645" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="I645" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J645" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="K645" t="n">
-        <v>0.78</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="L645" t="n">
-        <v>99.6399914979542</v>
+        <v>99.39422923641001</v>
       </c>
       <c r="M645" t="b">
         <v>0</v>
@@ -59801,52 +59771,47 @@
         <v>0</v>
       </c>
       <c r="O645" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P645" t="b">
         <v>0</v>
       </c>
       <c r="Q645" t="b">
-        <v>1</v>
-      </c>
-      <c r="R645" t="inlineStr">
-        <is>
-          <t>high_tedana_rejected_components</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S645" t="b">
         <v>1</v>
       </c>
       <c r="U645" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V645" t="inlineStr">
         <is>
-          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W645" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X645" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12047/ses-01/sub-12047_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y645" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12047/ses-01/func/sub-12047_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -59870,25 +59835,25 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>53.49885014863685</v>
+        <v>30.91064093692694</v>
       </c>
       <c r="G646" t="n">
-        <v>0.1332510791776314</v>
+        <v>0.3061122550998683</v>
       </c>
       <c r="H646" t="n">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="I646" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J646" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="K646" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="L646" t="n">
-        <v>99.14846697486583</v>
+        <v>99.70242839683299</v>
       </c>
       <c r="M646" t="b">
         <v>0</v>
@@ -59897,17 +59862,17 @@
         <v>0</v>
       </c>
       <c r="O646" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P646" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q646" t="b">
         <v>1</v>
       </c>
       <c r="R646" t="inlineStr">
         <is>
-          <t>low_brain_coverage</t>
+          <t>high_tedana_rejected_components</t>
         </is>
       </c>
       <c r="S646" t="b">
@@ -59920,29 +59885,29 @@
       </c>
       <c r="V646" t="inlineStr">
         <is>
-          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W646" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X646" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y646" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -59966,25 +59931,25 @@
         </is>
       </c>
       <c r="F647" t="n">
-        <v>48.44328886829317</v>
+        <v>28.32871760160197</v>
       </c>
       <c r="G647" t="n">
-        <v>0.144711205721414</v>
+        <v>0.2903349328589003</v>
       </c>
       <c r="H647" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I647" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J647" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="K647" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="L647" t="n">
-        <v>99.61209416015728</v>
+        <v>99.6399914979542</v>
       </c>
       <c r="M647" t="b">
         <v>0</v>
@@ -59993,47 +59958,52 @@
         <v>0</v>
       </c>
       <c r="O647" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P647" t="b">
         <v>0</v>
       </c>
       <c r="Q647" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>high_tedana_rejected_components</t>
+        </is>
       </c>
       <c r="S647" t="b">
         <v>1</v>
       </c>
       <c r="U647" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V647" t="inlineStr">
         <is>
-          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W647" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X647" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12049/ses-01/sub-12049_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12049/ses-01/func/sub-12049_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -60057,25 +60027,25 @@
         </is>
       </c>
       <c r="F648" t="n">
-        <v>45.51768332021311</v>
+        <v>53.49885014863685</v>
       </c>
       <c r="G648" t="n">
-        <v>0.1415992202242452</v>
+        <v>0.1332510791776314</v>
       </c>
       <c r="H648" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I648" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J648" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K648" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L648" t="n">
-        <v>98.70742334874329</v>
+        <v>99.14846697486583</v>
       </c>
       <c r="M648" t="b">
         <v>0</v>
@@ -60107,29 +60077,29 @@
       </c>
       <c r="V648" t="inlineStr">
         <is>
-          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W648" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X648" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -60153,25 +60123,25 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>53.94919102569111</v>
+        <v>48.44328886829317</v>
       </c>
       <c r="G649" t="n">
-        <v>0.1026628483699073</v>
+        <v>0.144711205721414</v>
       </c>
       <c r="H649" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I649" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J649" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K649" t="n">
-        <v>0.525</v>
+        <v>0.5</v>
       </c>
       <c r="L649" t="n">
-        <v>98.96514161220044</v>
+        <v>99.61209416015728</v>
       </c>
       <c r="M649" t="b">
         <v>0</v>
@@ -60183,49 +60153,44 @@
         <v>0</v>
       </c>
       <c r="P649" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q649" t="b">
-        <v>1</v>
-      </c>
-      <c r="R649" t="inlineStr">
-        <is>
-          <t>low_brain_coverage</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S649" t="b">
         <v>1</v>
       </c>
       <c r="U649" t="inlineStr">
         <is>
-          <t>outlier</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V649" t="inlineStr">
         <is>
-          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W649" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X649" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12051/ses-01/sub-12051_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y649" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12051/ses-01/func/sub-12051_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -60249,25 +60214,25 @@
         </is>
       </c>
       <c r="F650" t="n">
-        <v>51.80856852419674</v>
+        <v>45.51768332021311</v>
       </c>
       <c r="G650" t="n">
-        <v>0.09047883923297501</v>
+        <v>0.1415992202242452</v>
       </c>
       <c r="H650" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="I650" t="n">
         <v>17</v>
       </c>
       <c r="J650" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K650" t="n">
-        <v>0.32</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="L650" t="n">
-        <v>99.78612041022372</v>
+        <v>98.70742334874329</v>
       </c>
       <c r="M650" t="b">
         <v>0</v>
@@ -60279,44 +60244,49 @@
         <v>0</v>
       </c>
       <c r="P650" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q650" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>low_brain_coverage</t>
+        </is>
       </c>
       <c r="S650" t="b">
         <v>1</v>
       </c>
       <c r="U650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V650" t="inlineStr">
         <is>
-          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W650" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X650" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -60340,25 +60310,25 @@
         </is>
       </c>
       <c r="F651" t="n">
-        <v>54.0980097935535</v>
+        <v>53.94919102569111</v>
       </c>
       <c r="G651" t="n">
-        <v>0.104961722701671</v>
+        <v>0.1026628483699073</v>
       </c>
       <c r="H651" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I651" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J651" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K651" t="n">
-        <v>0.391304347826087</v>
+        <v>0.525</v>
       </c>
       <c r="L651" t="n">
-        <v>99.83925819650354</v>
+        <v>98.96514161220044</v>
       </c>
       <c r="M651" t="b">
         <v>0</v>
@@ -60370,134 +60340,321 @@
         <v>0</v>
       </c>
       <c r="P651" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q651" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>low_brain_coverage</t>
+        </is>
       </c>
       <c r="S651" t="b">
         <v>1</v>
       </c>
       <c r="U651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>outlier</t>
         </is>
       </c>
       <c r="V651" t="inlineStr">
         <is>
-          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+          <t>bids/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
       <c r="W651" t="inlineStr">
         <is>
-          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+          <t>derivatives/mriqc/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
         </is>
       </c>
       <c r="X651" t="inlineStr">
         <is>
-          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+          <t>derivatives/tedana/sub-12054/ses-01/sub-12054_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y651" t="inlineStr">
         <is>
-          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+          <t>derivatives/fmriprep/sub-12054/ses-01/func/sub-12054_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
+          <t>12055</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>51.80856852419674</v>
+      </c>
+      <c r="G652" t="n">
+        <v>0.09047883923297501</v>
+      </c>
+      <c r="H652" t="n">
+        <v>25</v>
+      </c>
+      <c r="I652" t="n">
+        <v>17</v>
+      </c>
+      <c r="J652" t="n">
+        <v>8</v>
+      </c>
+      <c r="K652" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L652" t="n">
+        <v>99.78612041022372</v>
+      </c>
+      <c r="M652" t="b">
+        <v>0</v>
+      </c>
+      <c r="N652" t="b">
+        <v>0</v>
+      </c>
+      <c r="O652" t="b">
+        <v>0</v>
+      </c>
+      <c r="P652" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q652" t="b">
+        <v>0</v>
+      </c>
+      <c r="S652" t="b">
+        <v>1</v>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
+        </is>
+      </c>
+      <c r="W652" t="inlineStr">
+        <is>
+          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X652" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
+        </is>
+      </c>
+      <c r="Y652" t="inlineStr">
+        <is>
+          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>12055</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>54.0980097935535</v>
+      </c>
+      <c r="G653" t="n">
+        <v>0.104961722701671</v>
+      </c>
+      <c r="H653" t="n">
+        <v>23</v>
+      </c>
+      <c r="I653" t="n">
+        <v>14</v>
+      </c>
+      <c r="J653" t="n">
+        <v>9</v>
+      </c>
+      <c r="K653" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="L653" t="n">
+        <v>99.83925819650354</v>
+      </c>
+      <c r="M653" t="b">
+        <v>0</v>
+      </c>
+      <c r="N653" t="b">
+        <v>0</v>
+      </c>
+      <c r="O653" t="b">
+        <v>0</v>
+      </c>
+      <c r="P653" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q653" t="b">
+        <v>0</v>
+      </c>
+      <c r="S653" t="b">
+        <v>1</v>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>bids/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.nii.gz</t>
+        </is>
+      </c>
+      <c r="W653" t="inlineStr">
+        <is>
+          <t>derivatives/mriqc/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X653" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-12055/ses-01/sub-12055_ses-01_task-trust_run-2_desc-tedana_metrics.tsv</t>
+        </is>
+      </c>
+      <c r="Y653" t="inlineStr">
+        <is>
+          <t>derivatives/fmriprep/sub-12055/ses-01/func/sub-12055_ses-01_task-trust_run-2_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
           <t>12057</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="D652" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr">
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F652" t="n">
+      <c r="F654" t="n">
         <v>65.82148309098557</v>
       </c>
-      <c r="G652" t="n">
+      <c r="G654" t="n">
         <v>0.08265729611933353</v>
       </c>
-      <c r="H652" t="n">
+      <c r="H654" t="n">
         <v>27</v>
       </c>
-      <c r="I652" t="n">
+      <c r="I654" t="n">
         <v>14</v>
       </c>
-      <c r="J652" t="n">
+      <c r="J654" t="n">
         <v>13</v>
       </c>
-      <c r="K652" t="n">
+      <c r="K654" t="n">
         <v>0.4814814814814815</v>
       </c>
-      <c r="L652" t="n">
+      <c r="L654" t="n">
         <v>99.29326744247835</v>
       </c>
-      <c r="M652" t="b">
-        <v>0</v>
-      </c>
-      <c r="N652" t="b">
-        <v>0</v>
-      </c>
-      <c r="O652" t="b">
-        <v>0</v>
-      </c>
-      <c r="P652" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q652" t="b">
-        <v>0</v>
-      </c>
-      <c r="S652" t="b">
-        <v>1</v>
-      </c>
-      <c r="U652" t="inlineStr">
+      <c r="M654" t="b">
+        <v>0</v>
+      </c>
+      <c r="N654" t="b">
+        <v>0</v>
+      </c>
+      <c r="O654" t="b">
+        <v>0</v>
+      </c>
+      <c r="P654" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q654" t="b">
+        <v>0</v>
+      </c>
+      <c r="S654" t="b">
+        <v>1</v>
+      </c>
+      <c r="U654" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="V652" t="inlineStr">
+      <c r="V654" t="inlineStr">
         <is>
           <t>bids/sub-12057/ses-01/func/sub-12057_ses-01_task-trust_run-1_echo-2_part-mag_bold.nii.gz</t>
         </is>
       </c>
-      <c r="W652" t="inlineStr">
+      <c r="W654" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-12057/ses-01/func/sub-12057_ses-01_task-trust_run-1_echo-2_part-mag_bold.json</t>
         </is>
       </c>
-      <c r="X652" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>derivatives/tedana/sub-12057/ses-01/sub-12057_ses-01_task-trust_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
-      <c r="Y652" t="inlineStr">
+      <c r="Y654" t="inlineStr">
         <is>
           <t>derivatives/fmriprep/sub-12057/ses-01/func/sub-12057_ses-01_task-trust_run-1_part-mag_space-MNI152NLin6Asym_desc-brain_mask.nii.gz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y652"/>
-  <conditionalFormatting sqref="A2:Y652">
+  <autoFilter ref="A1:Y654"/>
+  <conditionalFormatting sqref="A2:Y654">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$Q2=TRUE</formula>
     </cfRule>
@@ -60605,22 +60762,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E2" t="n">
-        <v>23.60912652261322</v>
+        <v>23.74153487046715</v>
       </c>
       <c r="F2" t="n">
-        <v>39.1948999002343</v>
+        <v>39.23184253158979</v>
       </c>
       <c r="G2" t="n">
-        <v>15.58577337762108</v>
+        <v>15.49030766112264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2304664561816026</v>
+        <v>0.506073378783185</v>
       </c>
       <c r="I2" t="n">
-        <v>62.57355996666593</v>
+        <v>62.46730402327375</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -60648,22 +60805,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1237710602220436</v>
+        <v>0.1239379801643464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.245989755381984</v>
+        <v>0.245951639409154</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1222186951599404</v>
+        <v>0.1220136592448076</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05955698251786697</v>
+        <v>-0.05908250870286505</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4293177981218946</v>
+        <v>0.4289721282763654</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -60691,22 +60848,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.75</v>
+        <v>-10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>40.25</v>
+        <v>41.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -60714,7 +60871,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -60734,22 +60891,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E5" t="n">
-        <v>99.61873638344227</v>
+        <v>99.61209416015728</v>
       </c>
       <c r="F5" t="n">
         <v>99.9096657633243</v>
       </c>
       <c r="G5" t="n">
-        <v>0.29092937988203</v>
+        <v>0.2975716031670146</v>
       </c>
       <c r="H5" t="n">
-        <v>99.18234231361922</v>
+        <v>99.16573675540675</v>
       </c>
       <c r="I5" t="n">
-        <v>100.3460598331473</v>
+        <v>100.3560231680748</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -60757,7 +60914,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
